--- a/exports_hebdomadaires/export_2026-08-10.xlsx
+++ b/exports_hebdomadaires/export_2026-08-10.xlsx
@@ -1164,6 +1164,11 @@
           <t>EMY-500162</t>
         </is>
       </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE6" t="inlineStr">
         <is>
           <t>Kristelle absente tout le mois (congés).</t>
@@ -3838,6 +3843,11 @@
           <t>EMY-500237</t>
         </is>
       </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE29" t="inlineStr">
         <is>
           <t>Kristelle absente tout le mois (congés).</t>
@@ -4099,6 +4109,11 @@
           <t>EMY-500793</t>
         </is>
       </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>MAC-018</t>
+        </is>
+      </c>
       <c r="AE31" t="inlineStr">
         <is>
           <t>Kristelle absente tout le mois (congés).</t>
@@ -6953,6 +6968,11 @@
           <t>EMY-500749</t>
         </is>
       </c>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE55" t="inlineStr">
         <is>
           <t>Kristelle absente tout le mois (congés).</t>
@@ -8584,6 +8604,11 @@
           <t>EMY-500278</t>
         </is>
       </c>
+      <c r="AD69" t="inlineStr">
+        <is>
+          <t>MAC-018</t>
+        </is>
+      </c>
       <c r="AE69" t="inlineStr">
         <is>
           <t>Kristelle absente tout le mois (congés).</t>
@@ -9754,6 +9779,11 @@
           <t>EMY-500200</t>
         </is>
       </c>
+      <c r="AD79" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE79" t="inlineStr">
         <is>
           <t>Kristelle absente tout le mois (congés).</t>
@@ -11426,6 +11456,11 @@
           <t>EMY-500395</t>
         </is>
       </c>
+      <c r="AD93" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE93" t="inlineStr">
         <is>
           <t>Kristelle absente tout le mois (congés).</t>
@@ -13791,6 +13826,11 @@
           <t>EMY-500200</t>
         </is>
       </c>
+      <c r="AD112" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE112" t="inlineStr">
         <is>
           <t>Kristelle absente tout le mois (congés).</t>
@@ -18045,6 +18085,11 @@
           <t>EMY-500645</t>
         </is>
       </c>
+      <c r="AD148" t="inlineStr">
+        <is>
+          <t>MAC-018</t>
+        </is>
+      </c>
       <c r="AE148" t="inlineStr">
         <is>
           <t>Kristelle absente tout le mois (congés).</t>
@@ -19430,6 +19475,11 @@
           <t>EMY-500218</t>
         </is>
       </c>
+      <c r="AD160" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE160" t="inlineStr">
         <is>
           <t>Kristelle absente tout le mois (congés).</t>
@@ -25117,6 +25167,11 @@
           <t>EMY-500505</t>
         </is>
       </c>
+      <c r="AD207" t="inlineStr">
+        <is>
+          <t>MAC-018</t>
+        </is>
+      </c>
       <c r="AE207" t="inlineStr">
         <is>
           <t>Kristelle absente tout le mois (congés).</t>
@@ -25231,6 +25286,11 @@
           <t>EMY-500831</t>
         </is>
       </c>
+      <c r="AD208" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE208" t="inlineStr">
         <is>
           <t>Kristelle absente tout le mois (congés).</t>
@@ -26898,6 +26958,11 @@
           <t>EMY-500200</t>
         </is>
       </c>
+      <c r="AD222" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE222" t="inlineStr">
         <is>
           <t>Kristelle absente tout le mois (congés).</t>
@@ -27260,6 +27325,11 @@
           <t>EMY-500598</t>
         </is>
       </c>
+      <c r="AD225" t="inlineStr">
+        <is>
+          <t>MAC-018</t>
+        </is>
+      </c>
       <c r="AE225" t="inlineStr">
         <is>
           <t>Kristelle absente tout le mois (congés).</t>
@@ -27825,6 +27895,11 @@
           <t>EMY-500395</t>
         </is>
       </c>
+      <c r="AD230" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE230" t="inlineStr">
         <is>
           <t>Kristelle absente tout le mois (congés).</t>
@@ -30515,6 +30590,11 @@
           <t>EMY-500645</t>
         </is>
       </c>
+      <c r="AD253" t="inlineStr">
+        <is>
+          <t>MAC-018</t>
+        </is>
+      </c>
       <c r="AE253" t="inlineStr">
         <is>
           <t>Kristelle absente tout le mois (congés).</t>
@@ -31007,6 +31087,11 @@
           <t>EMY-500721</t>
         </is>
       </c>
+      <c r="AD257" t="inlineStr">
+        <is>
+          <t>MAC-018</t>
+        </is>
+      </c>
       <c r="AE257" t="inlineStr">
         <is>
           <t>Kristelle absente tout le mois (congés).</t>
@@ -31121,6 +31206,11 @@
           <t>EMY-500597</t>
         </is>
       </c>
+      <c r="AD258" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE258" t="inlineStr">
         <is>
           <t>Kristelle absente tout le mois (congés).</t>
@@ -42135,6 +42225,11 @@
           <t>EMY-500664</t>
         </is>
       </c>
+      <c r="AD351" t="inlineStr">
+        <is>
+          <t>MAC-018</t>
+        </is>
+      </c>
       <c r="AE351" t="inlineStr">
         <is>
           <t>Kristelle absente tout le mois (congés).</t>
@@ -42267,6 +42362,11 @@
           <t>EMY-500111</t>
         </is>
       </c>
+      <c r="AD352" t="inlineStr">
+        <is>
+          <t>MAC-018</t>
+        </is>
+      </c>
       <c r="AE352" t="inlineStr">
         <is>
           <t>Kristelle absente tout le mois (congés).</t>
@@ -43878,6 +43978,11 @@
           <t>EMY-500420</t>
         </is>
       </c>
+      <c r="AD366" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE366" t="inlineStr">
         <is>
           <t>Kristelle absente tout le mois (congés).</t>
@@ -44481,6 +44586,11 @@
           <t>EMY-500818</t>
         </is>
       </c>
+      <c r="AD371" t="inlineStr">
+        <is>
+          <t>MAC-018</t>
+        </is>
+      </c>
       <c r="AE371" t="inlineStr">
         <is>
           <t>Kristelle absente tout le mois (congés).</t>
@@ -45105,6 +45215,11 @@
           <t>EMY-500274</t>
         </is>
       </c>
+      <c r="AD376" t="inlineStr">
+        <is>
+          <t>MAC-018</t>
+        </is>
+      </c>
       <c r="AE376" t="inlineStr">
         <is>
           <t>Kristelle absente tout le mois (congés).</t>
@@ -45338,6 +45453,11 @@
           <t>EMY-500060</t>
         </is>
       </c>
+      <c r="AD378" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE378" t="inlineStr">
         <is>
           <t>Kristelle absente tout le mois (congés).</t>
@@ -45905,6 +46025,11 @@
           <t>EMY-500796</t>
         </is>
       </c>
+      <c r="AD383" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE383" t="inlineStr">
         <is>
           <t>Kristelle absente tout le mois (congés).</t>
@@ -48392,6 +48517,11 @@
           <t>EMY-500420</t>
         </is>
       </c>
+      <c r="AD404" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE404" t="inlineStr">
         <is>
           <t>Kristelle absente tout le mois (congés).</t>
@@ -49838,6 +49968,11 @@
           <t>EMY-500721</t>
         </is>
       </c>
+      <c r="AD416" t="inlineStr">
+        <is>
+          <t>MAC-018</t>
+        </is>
+      </c>
       <c r="AE416" t="inlineStr">
         <is>
           <t>Kristelle absente tout le mois (congés).</t>
@@ -52953,6 +53088,11 @@
           <t>EMY-500409</t>
         </is>
       </c>
+      <c r="AD442" t="inlineStr">
+        <is>
+          <t>MAC-018</t>
+        </is>
+      </c>
       <c r="AE442" t="inlineStr">
         <is>
           <t>Kristelle absente tout le mois (congés).</t>
@@ -53665,6 +53805,11 @@
           <t>EMY-500490</t>
         </is>
       </c>
+      <c r="AD448" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE448" t="inlineStr">
         <is>
           <t>Kristelle absente tout le mois (congés).</t>
@@ -59058,6 +59203,11 @@
           <t>EMY-500448</t>
         </is>
       </c>
+      <c r="AD493" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE493" t="inlineStr">
         <is>
           <t>Kristelle absente tout le mois (congés).</t>
@@ -59167,6 +59317,11 @@
           <t>EMY-500177</t>
         </is>
       </c>
+      <c r="AD494" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE494" t="inlineStr">
         <is>
           <t>Kristelle absente tout le mois (congés).</t>
@@ -63461,6 +63616,11 @@
           <t>EMY-500803</t>
         </is>
       </c>
+      <c r="AD530" t="inlineStr">
+        <is>
+          <t>MAC-018</t>
+        </is>
+      </c>
       <c r="AE530" t="inlineStr">
         <is>
           <t>Kristelle absente tout le mois (congés).</t>
@@ -68906,6 +69066,11 @@
           <t>EMY-500237</t>
         </is>
       </c>
+      <c r="AD576" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
+        </is>
+      </c>
       <c r="AE576" t="inlineStr">
         <is>
           <t>Kristelle absente tout le mois (congés).</t>
@@ -70218,6 +70383,11 @@
       <c r="AC587" t="inlineStr">
         <is>
           <t>EMY-500476</t>
+        </is>
+      </c>
+      <c r="AD587" t="inlineStr">
+        <is>
+          <t>MAC-017</t>
         </is>
       </c>
       <c r="AE587" t="inlineStr">

--- a/exports_hebdomadaires/export_2026-08-10.xlsx
+++ b/exports_hebdomadaires/export_2026-08-10.xlsx
@@ -694,7 +694,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG2" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG3" t="n">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG7" t="n">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG20" t="n">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG22" t="n">
@@ -3055,7 +3055,7 @@
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG24" t="n">
@@ -3820,7 +3820,7 @@
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG31" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG36" t="n">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG40" t="n">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG44" t="n">
@@ -5327,7 +5327,7 @@
       </c>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG45" t="n">
@@ -5877,7 +5877,7 @@
       </c>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG50" t="n">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG52" t="n">
@@ -6455,7 +6455,7 @@
       </c>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG55" t="n">
@@ -6559,7 +6559,7 @@
       </c>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG56" t="n">
@@ -6977,7 +6977,7 @@
       </c>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG60" t="n">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="AF61" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG61" t="n">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="AF63" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG63" t="n">
@@ -7782,7 +7782,7 @@
       </c>
       <c r="AF68" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG68" t="n">
@@ -8005,7 +8005,7 @@
       </c>
       <c r="AF70" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG70" t="n">
@@ -8114,7 +8114,7 @@
       </c>
       <c r="AF71" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG71" t="n">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="AF72" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG72" t="n">
@@ -8335,7 +8335,7 @@
       </c>
       <c r="AF73" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG73" t="n">
@@ -8740,7 +8740,7 @@
       </c>
       <c r="AF77" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG77" t="n">
@@ -9062,7 +9062,7 @@
       </c>
       <c r="AF80" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG80" t="n">
@@ -9523,7 +9523,7 @@
       </c>
       <c r="AF84" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG84" t="n">
@@ -9731,7 +9731,7 @@
       </c>
       <c r="AF86" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG86" t="n">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="AF88" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG88" t="n">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="AF91" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG91" t="n">
@@ -10360,7 +10360,7 @@
       </c>
       <c r="AF92" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG92" t="n">
@@ -10464,7 +10464,7 @@
       </c>
       <c r="AF93" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG93" t="n">
@@ -10659,7 +10659,7 @@
       </c>
       <c r="AF95" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG95" t="n">
@@ -10986,7 +10986,7 @@
       </c>
       <c r="AF98" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG98" t="n">
@@ -11328,7 +11328,7 @@
       </c>
       <c r="AF101" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG101" t="n">
@@ -11660,7 +11660,7 @@
       </c>
       <c r="AF104" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG104" t="n">
@@ -11769,7 +11769,7 @@
       </c>
       <c r="AF105" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG105" t="n">
@@ -11992,7 +11992,7 @@
       </c>
       <c r="AF107" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG107" t="n">
@@ -12096,7 +12096,7 @@
       </c>
       <c r="AF108" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG108" t="n">
@@ -12436,7 +12436,7 @@
       </c>
       <c r="AF111" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG111" t="n">
@@ -12867,7 +12867,7 @@
       </c>
       <c r="AF115" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG115" t="n">
@@ -13287,7 +13287,7 @@
       </c>
       <c r="AF119" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG119" t="n">
@@ -13505,7 +13505,7 @@
       </c>
       <c r="AF121" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG121" t="n">
@@ -13705,7 +13705,7 @@
       </c>
       <c r="AF123" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG123" t="n">
@@ -14390,7 +14390,7 @@
       </c>
       <c r="AF129" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG129" t="n">
@@ -15279,7 +15279,7 @@
       </c>
       <c r="AF138" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG138" t="n">
@@ -15383,7 +15383,7 @@
       </c>
       <c r="AF139" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG139" t="n">
@@ -15728,7 +15728,7 @@
       </c>
       <c r="AF142" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG142" t="n">
@@ -15941,7 +15941,7 @@
       </c>
       <c r="AF144" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG144" t="n">
@@ -16336,7 +16336,7 @@
       </c>
       <c r="AF148" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG148" t="n">
@@ -16445,7 +16445,7 @@
       </c>
       <c r="AF149" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG149" t="n">
@@ -16863,7 +16863,7 @@
       </c>
       <c r="AF153" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG153" t="n">
@@ -16967,7 +16967,7 @@
       </c>
       <c r="AF154" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG154" t="n">
@@ -17079,7 +17079,7 @@
       </c>
       <c r="AF155" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG155" t="n">
@@ -18155,7 +18155,7 @@
       </c>
       <c r="AF165" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG165" t="n">
@@ -19104,7 +19104,7 @@
       </c>
       <c r="AF173" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG173" t="n">
@@ -19831,7 +19831,7 @@
       </c>
       <c r="AF180" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG180" t="n">
@@ -20044,7 +20044,7 @@
       </c>
       <c r="AF182" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG182" t="n">
@@ -20897,7 +20897,7 @@
       </c>
       <c r="AF190" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG190" t="n">
@@ -21442,7 +21442,7 @@
       </c>
       <c r="AF195" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG195" t="n">
@@ -21546,7 +21546,7 @@
       </c>
       <c r="AF196" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG196" t="n">
@@ -21774,7 +21774,7 @@
       </c>
       <c r="AF198" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG198" t="n">
@@ -21878,7 +21878,7 @@
       </c>
       <c r="AF199" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG199" t="n">
@@ -22316,7 +22316,7 @@
       </c>
       <c r="AF203" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG203" t="n">
@@ -22420,7 +22420,7 @@
       </c>
       <c r="AF204" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG204" t="n">
@@ -22532,7 +22532,7 @@
       </c>
       <c r="AF205" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG205" t="n">
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AF208" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG208" t="n">
@@ -22971,7 +22971,7 @@
       </c>
       <c r="AF209" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG209" t="n">
@@ -23923,7 +23923,7 @@
       </c>
       <c r="AF218" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG218" t="n">
@@ -24027,7 +24027,7 @@
       </c>
       <c r="AF219" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG219" t="n">
@@ -24144,7 +24144,7 @@
       </c>
       <c r="AF220" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG220" t="n">
@@ -25020,7 +25020,7 @@
       </c>
       <c r="AF228" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG228" t="n">
@@ -25230,7 +25230,7 @@
       </c>
       <c r="AF230" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG230" t="n">
@@ -25339,7 +25339,7 @@
       </c>
       <c r="AF231" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG231" t="n">
@@ -25664,7 +25664,7 @@
       </c>
       <c r="AF234" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG234" t="n">
@@ -25768,7 +25768,7 @@
       </c>
       <c r="AF235" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG235" t="n">
@@ -25872,7 +25872,7 @@
       </c>
       <c r="AF236" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG236" t="n">
@@ -25976,7 +25976,7 @@
       </c>
       <c r="AF237" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG237" t="n">
@@ -26323,7 +26323,7 @@
       </c>
       <c r="AF240" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG240" t="n">
@@ -26622,7 +26622,7 @@
       </c>
       <c r="AF243" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG243" t="n">
@@ -26726,7 +26726,7 @@
       </c>
       <c r="AF244" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG244" t="n">
@@ -26835,7 +26835,7 @@
       </c>
       <c r="AF245" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG245" t="n">
@@ -26947,7 +26947,7 @@
       </c>
       <c r="AF246" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG246" t="n">
@@ -27064,7 +27064,7 @@
       </c>
       <c r="AF247" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG247" t="n">
@@ -27530,7 +27530,7 @@
       </c>
       <c r="AF251" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG251" t="n">
@@ -27634,7 +27634,7 @@
       </c>
       <c r="AF252" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG252" t="n">
@@ -27834,7 +27834,7 @@
       </c>
       <c r="AF254" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG254" t="n">
@@ -28171,7 +28171,7 @@
       </c>
       <c r="AF257" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG257" t="n">
@@ -28280,7 +28280,7 @@
       </c>
       <c r="AF258" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG258" t="n">
@@ -29364,7 +29364,7 @@
       </c>
       <c r="AF268" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG268" t="n">
@@ -29823,7 +29823,7 @@
       </c>
       <c r="AF272" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG272" t="n">
@@ -30251,7 +30251,7 @@
       </c>
       <c r="AF276" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG276" t="n">
@@ -30355,7 +30355,7 @@
       </c>
       <c r="AF277" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG277" t="n">
@@ -30692,7 +30692,7 @@
       </c>
       <c r="AF280" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG280" t="n">
@@ -30796,7 +30796,7 @@
       </c>
       <c r="AF281" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG281" t="n">
@@ -31242,7 +31242,7 @@
       </c>
       <c r="AF285" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG285" t="n">
@@ -31447,7 +31447,7 @@
       </c>
       <c r="AF287" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG287" t="n">
@@ -31647,7 +31647,7 @@
       </c>
       <c r="AF289" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG289" t="n">
@@ -31852,7 +31852,7 @@
       </c>
       <c r="AF291" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG291" t="n">
@@ -32052,7 +32052,7 @@
       </c>
       <c r="AF293" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG293" t="n">
@@ -32265,7 +32265,7 @@
       </c>
       <c r="AF295" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG295" t="n">
@@ -32369,7 +32369,7 @@
       </c>
       <c r="AF296" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG296" t="n">
@@ -32473,7 +32473,7 @@
       </c>
       <c r="AF297" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG297" t="n">
@@ -32582,7 +32582,7 @@
       </c>
       <c r="AF298" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG298" t="n">
@@ -32790,7 +32790,7 @@
       </c>
       <c r="AF300" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG300" t="n">
@@ -32985,7 +32985,7 @@
       </c>
       <c r="AF302" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG302" t="n">
@@ -33714,7 +33714,7 @@
       </c>
       <c r="AF309" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG309" t="n">
@@ -33818,7 +33818,7 @@
       </c>
       <c r="AF310" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG310" t="n">
@@ -34023,7 +34023,7 @@
       </c>
       <c r="AF312" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG312" t="n">
@@ -34127,7 +34127,7 @@
       </c>
       <c r="AF313" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG313" t="n">
@@ -34322,7 +34322,7 @@
       </c>
       <c r="AF315" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG315" t="n">
@@ -34434,7 +34434,7 @@
       </c>
       <c r="AF316" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG316" t="n">
@@ -34551,7 +34551,7 @@
       </c>
       <c r="AF317" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG317" t="n">
@@ -34660,7 +34660,7 @@
       </c>
       <c r="AF318" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG318" t="n">
@@ -35208,7 +35208,7 @@
       </c>
       <c r="AF323" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG323" t="n">
@@ -35571,7 +35571,7 @@
       </c>
       <c r="AF326" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG326" t="n">
@@ -36321,7 +36321,7 @@
       </c>
       <c r="AF333" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG333" t="n">
@@ -37298,7 +37298,7 @@
       </c>
       <c r="AF342" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG342" t="n">
@@ -37759,7 +37759,7 @@
       </c>
       <c r="AF346" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG346" t="n">
@@ -38311,7 +38311,7 @@
       </c>
       <c r="AF351" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG351" t="n">
@@ -38415,7 +38415,7 @@
       </c>
       <c r="AF352" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG352" t="n">
@@ -38519,7 +38519,7 @@
       </c>
       <c r="AF353" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG353" t="n">
@@ -38631,7 +38631,7 @@
       </c>
       <c r="AF354" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG354" t="n">
@@ -39041,7 +39041,7 @@
       </c>
       <c r="AF358" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG358" t="n">
@@ -39371,7 +39371,7 @@
       </c>
       <c r="AF361" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG361" t="n">
@@ -39716,7 +39716,7 @@
       </c>
       <c r="AF364" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG364" t="n">
@@ -40808,7 +40808,7 @@
       </c>
       <c r="AF374" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG374" t="n">
@@ -41231,7 +41231,7 @@
       </c>
       <c r="AF378" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG378" t="n">
@@ -41439,7 +41439,7 @@
       </c>
       <c r="AF380" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG380" t="n">
@@ -41865,7 +41865,7 @@
       </c>
       <c r="AF384" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG384" t="n">
@@ -42070,7 +42070,7 @@
       </c>
       <c r="AF386" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG386" t="n">
@@ -42187,7 +42187,7 @@
       </c>
       <c r="AF387" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG387" t="n">
@@ -43206,7 +43206,7 @@
       </c>
       <c r="AF396" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG396" t="n">
@@ -43323,7 +43323,7 @@
       </c>
       <c r="AF397" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG397" t="n">
@@ -44317,7 +44317,7 @@
       </c>
       <c r="AF406" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG406" t="n">
@@ -44429,7 +44429,7 @@
       </c>
       <c r="AF407" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG407" t="n">
@@ -44538,7 +44538,7 @@
       </c>
       <c r="AF408" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG408" t="n">
@@ -44766,7 +44766,7 @@
       </c>
       <c r="AF410" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG410" t="n">
@@ -44883,7 +44883,7 @@
       </c>
       <c r="AF411" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG411" t="n">
@@ -45220,7 +45220,7 @@
       </c>
       <c r="AF414" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG414" t="n">
@@ -45324,7 +45324,7 @@
       </c>
       <c r="AF415" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG415" t="n">
@@ -46309,7 +46309,7 @@
       </c>
       <c r="AF424" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG424" t="n">
@@ -46793,7 +46793,7 @@
       </c>
       <c r="AF428" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG428" t="n">
@@ -47411,7 +47411,7 @@
       </c>
       <c r="AF434" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG434" t="n">
@@ -48026,7 +48026,7 @@
       </c>
       <c r="AF440" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG440" t="n">
@@ -48897,7 +48897,7 @@
       </c>
       <c r="AF448" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG448" t="n">
@@ -49317,7 +49317,7 @@
       </c>
       <c r="AF452" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG452" t="n">
@@ -49649,7 +49649,7 @@
       </c>
       <c r="AF455" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG455" t="n">
@@ -50077,7 +50077,7 @@
       </c>
       <c r="AF459" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG459" t="n">
@@ -50371,7 +50371,7 @@
       </c>
       <c r="AF462" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG462" t="n">
@@ -51356,7 +51356,7 @@
       </c>
       <c r="AF471" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG471" t="n">
@@ -52133,7 +52133,7 @@
       </c>
       <c r="AF478" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG478" t="n">
@@ -52237,7 +52237,7 @@
       </c>
       <c r="AF479" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG479" t="n">
@@ -52346,7 +52346,7 @@
       </c>
       <c r="AF480" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG480" t="n">
@@ -53111,7 +53111,7 @@
       </c>
       <c r="AF487" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG487" t="n">
@@ -53215,7 +53215,7 @@
       </c>
       <c r="AF488" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG488" t="n">
@@ -53418,7 +53418,7 @@
       </c>
       <c r="AF490" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG490" t="n">
@@ -53522,7 +53522,7 @@
       </c>
       <c r="AF491" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG491" t="n">
@@ -54485,7 +54485,7 @@
       </c>
       <c r="AF500" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG500" t="n">
@@ -54589,7 +54589,7 @@
       </c>
       <c r="AF501" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG501" t="n">
@@ -54701,7 +54701,7 @@
       </c>
       <c r="AF502" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG502" t="n">
@@ -55008,7 +55008,7 @@
       </c>
       <c r="AF505" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG505" t="n">
@@ -55117,7 +55117,7 @@
       </c>
       <c r="AF506" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG506" t="n">
@@ -55646,7 +55646,7 @@
       </c>
       <c r="AF511" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG511" t="n">
@@ -55864,7 +55864,7 @@
       </c>
       <c r="AF513" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG513" t="n">
@@ -56095,7 +56095,7 @@
       </c>
       <c r="AF515" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG515" t="n">
@@ -56523,7 +56523,7 @@
       </c>
       <c r="AF519" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG519" t="n">
@@ -56977,7 +56977,7 @@
       </c>
       <c r="AF523" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG523" t="n">
@@ -57089,7 +57089,7 @@
       </c>
       <c r="AF524" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG524" t="n">
@@ -57533,7 +57533,7 @@
       </c>
       <c r="AF528" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG528" t="n">
@@ -58194,7 +58194,7 @@
       </c>
       <c r="AF534" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG534" t="n">
@@ -58311,7 +58311,7 @@
       </c>
       <c r="AF535" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG535" t="n">
@@ -58420,7 +58420,7 @@
       </c>
       <c r="AF536" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG536" t="n">
@@ -58628,7 +58628,7 @@
       </c>
       <c r="AF538" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG538" t="n">
@@ -58740,7 +58740,7 @@
       </c>
       <c r="AF539" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG539" t="n">
@@ -58844,7 +58844,7 @@
       </c>
       <c r="AF540" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG540" t="n">
@@ -59409,7 +59409,7 @@
       </c>
       <c r="AF545" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG545" t="n">
@@ -59513,7 +59513,7 @@
       </c>
       <c r="AF546" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG546" t="n">
@@ -59713,7 +59713,7 @@
       </c>
       <c r="AF548" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG548" t="n">
@@ -59949,7 +59949,7 @@
       </c>
       <c r="AF550" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG550" t="n">
@@ -60294,7 +60294,7 @@
       </c>
       <c r="AF553" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG553" t="n">
@@ -60406,7 +60406,7 @@
       </c>
       <c r="AF554" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG554" t="n">
@@ -60510,7 +60510,7 @@
       </c>
       <c r="AF555" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG555" t="n">
@@ -60705,7 +60705,7 @@
       </c>
       <c r="AF557" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG557" t="n">
@@ -60809,7 +60809,7 @@
       </c>
       <c r="AF558" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG558" t="n">
@@ -61157,7 +61157,7 @@
       </c>
       <c r="AF561" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG561" t="n">
@@ -61673,7 +61673,7 @@
       </c>
       <c r="AF566" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG566" t="n">
@@ -62463,7 +62463,7 @@
       </c>
       <c r="AF573" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG573" t="n">
@@ -63101,7 +63101,7 @@
       </c>
       <c r="AF579" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG579" t="n">
@@ -63545,7 +63545,7 @@
       </c>
       <c r="AF583" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG583" t="n">
@@ -63867,7 +63867,7 @@
       </c>
       <c r="AF586" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG586" t="n">
@@ -63976,7 +63976,7 @@
       </c>
       <c r="AF587" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG587" t="n">
@@ -64080,7 +64080,7 @@
       </c>
       <c r="AF588" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG588" t="n">
@@ -64184,7 +64184,7 @@
       </c>
       <c r="AF589" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG589" t="n">
@@ -64293,7 +64293,7 @@
       </c>
       <c r="AF590" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Velox Express</t>
         </is>
       </c>
       <c r="AG590" t="n">
@@ -64501,7 +64501,7 @@
       </c>
       <c r="AF592" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG592" t="n">
@@ -64818,7 +64818,7 @@
       </c>
       <c r="AF595" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG595" t="n">
@@ -64922,7 +64922,7 @@
       </c>
       <c r="AF596" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG596" t="n">
@@ -65687,7 +65687,7 @@
       </c>
       <c r="AF603" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG603" t="n">
@@ -66125,7 +66125,7 @@
       </c>
       <c r="AF607" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG607" t="n">
@@ -66579,7 +66579,7 @@
       </c>
       <c r="AF611" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG611" t="n">
@@ -66774,7 +66774,7 @@
       </c>
       <c r="AF613" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG613" t="n">
@@ -67280,7 +67280,7 @@
       </c>
       <c r="AF618" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG618" t="n">
@@ -68263,7 +68263,7 @@
       </c>
       <c r="AF627" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG627" t="n">
@@ -68372,7 +68372,7 @@
       </c>
       <c r="AF628" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG628" t="n">
@@ -68476,7 +68476,7 @@
       </c>
       <c r="AF629" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG629" t="n">
@@ -68671,7 +68671,7 @@
       </c>
       <c r="AF631" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG631" t="n">
@@ -68783,7 +68783,7 @@
       </c>
       <c r="AF632" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG632" t="n">
@@ -68996,7 +68996,7 @@
       </c>
       <c r="AF634" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG634" t="n">
@@ -69105,7 +69105,7 @@
       </c>
       <c r="AF635" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG635" t="n">
@@ -69536,7 +69536,7 @@
       </c>
       <c r="AF639" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG639" t="n">
@@ -69891,7 +69891,7 @@
       </c>
       <c r="AF642" t="inlineStr">
         <is>
-          <t>TransEuro</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG642" t="n">
@@ -69995,7 +69995,7 @@
       </c>
       <c r="AF643" t="inlineStr">
         <is>
-          <t>RapidPost</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG643" t="n">
@@ -70352,7 +70352,7 @@
       </c>
       <c r="AF646" t="inlineStr">
         <is>
-          <t>ColisExpress</t>
+          <t>Noria Standard</t>
         </is>
       </c>
       <c r="AG646" t="n">
